--- a/CSH030Ex_Revision_Process.xlsx
+++ b/CSH030Ex_Revision_Process.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
   <si>
     <t>Release Version</t>
   </si>
@@ -511,6 +511,14 @@
   <si>
     <t>A_O를 항목명=값 형식의 ASCII Text로 변경함. SW_Version을 맨 앞에 배치하고 항목명에 _를 사용하며 숫자 표현의 소수점 형식을 통일함.
 10월 26일 추가 수정: Admin 모드에 SubMark Viewer를 추가하고 프레임별 검출 위치, 유효 상태 및 TX/TY 표시와 프레임 이동을 지원함. 검출 좌표 보관·로그와 피크 후보 정보 처리를 보완함. 프로그램 표시 버전은 26102301로 유지됨.</t>
+  </si>
+  <si>
+    <t>X축 측정값이 간헐적으로 튀는 현상</t>
+  </si>
+  <si>
+    <t>Top View 마크 검출용 우측 ROI 위치를 보정함. 수정 SW(4Line V26102601) 
+배포 완료. 이미지 8,000장 검증 결과 해당 현상이 재발하지 않음을 확인함.</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1281,13 +1289,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1611,7 +1619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D60"/>
+  <dimension ref="B2:D61"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
@@ -2247,15 +2255,26 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="2:4" ht="123.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="17" t="s">
+    <row r="60" spans="2:4" ht="123.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D60" s="19" t="s">
+      <c r="D60" s="16" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="17">
+        <v>26102601</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/CSH030Ex_Revision_Process.xlsx
+++ b/CSH030Ex_Revision_Process.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="146">
   <si>
     <t>Release Version</t>
   </si>
@@ -520,6 +520,15 @@
 배포 완료. 이미지 8,000장 검증 결과 해당 현상이 재발하지 않음을 확인함.</t>
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
+  <si>
+    <t>26102701</t>
+  </si>
+  <si>
+    <t>X축 측정값에 약 0.5~0.6 µm의 간헐적 튐 발생</t>
+  </si>
+  <si>
+    <t>V26102601의 ROI 위치 변경 후 실제 마크 에지까지의 여유가 부족한 것으로 확인됨. Top View 우측 수직 에지 검출용 기본 ROI 폭을 3 pixel 확대함. 수정 SW(4Line V26102701) 배포 완료. 이미지 16,000장 검증 결과 해당 현상이 재발하지 않음을 확인함.</t>
+  </si>
 </sst>
 </file>
 
@@ -531,7 +540,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -704,6 +713,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1237,7 +1252,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1289,13 +1304,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1619,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D61"/>
+  <dimension ref="B2:D62"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
@@ -2266,15 +2284,26 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="2:4" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="17">
+    <row r="61" spans="2:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="B61" s="5">
         <v>26102601</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="17" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/CSH030Ex_Revision_Process.xlsx
+++ b/CSH030Ex_Revision_Process.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="149">
   <si>
     <t>Release Version</t>
   </si>
@@ -528,6 +528,422 @@
   </si>
   <si>
     <t>V26102601의 ROI 위치 변경 후 실제 마크 에지까지의 여유가 부족한 것으로 확인됨. Top View 우측 수직 에지 검출용 기본 ROI 폭을 3 pixel 확대함. 수정 SW(4Line V26102701) 배포 완료. 이미지 16,000장 검증 결과 해당 현상이 재발하지 않음을 확인함.</t>
+  </si>
+  <si>
+    <t>26102801</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">8150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>측정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마지막</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몇장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Grab </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현상</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Grab </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재시도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시퀀스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -540,7 +956,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -719,6 +1135,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1637,7 +2060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D62"/>
+  <dimension ref="B2:D63"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
@@ -2306,6 +2729,17 @@
         <v>145</v>
       </c>
     </row>
+    <row r="63" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CSH030Ex_Revision_Process.xlsx
+++ b/CSH030Ex_Revision_Process.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\csh030ex_4line\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\git\csh030ex_4line\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="152">
   <si>
     <t>Release Version</t>
   </si>
@@ -942,6 +942,397 @@
         <charset val="129"/>
       </rPr>
       <t>추가</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>26103001</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간헐적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sweep </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상관없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마지막</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현상</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sweep </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마지막</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장하도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모니터링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예정</t>
     </r>
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
@@ -949,7 +1340,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -1330,7 +1721,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1491,37 +1882,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1675,7 +2035,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1730,14 +2090,17 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2060,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D63"/>
+  <dimension ref="B2:D64"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
@@ -2718,7 +3081,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="B62" s="18" t="s">
         <v>143</v>
       </c>
@@ -2729,19 +3092,31 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="18" t="s">
+    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B63" s="21" t="s">
         <v>146</v>
       </c>
       <c r="C63" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="19" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B64" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>